--- a/data/trans_orig/IP16A01-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16A01-Habitat-trans_orig.xlsx
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18240</t>
+          <t>19266</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27071</t>
+          <t>27148</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16295</t>
+          <t>16411</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26035</t>
+          <t>25973</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37753</t>
+          <t>38470</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51306</t>
+          <t>50845</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,19%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>4298</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13206</t>
+          <t>12180</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8389</t>
+          <t>8451</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18129</t>
+          <t>18013</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14564</t>
+          <t>15025</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28117</t>
+          <t>27400</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>41,6%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19798</t>
+          <t>19417</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29474</t>
+          <t>29208</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17083</t>
+          <t>17168</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27552</t>
+          <t>27827</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39585</t>
+          <t>39623</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53572</t>
+          <t>53491</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,1%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11127</t>
+          <t>11393</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20803</t>
+          <t>21184</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12768</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23237</t>
+          <t>23152</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>27349</t>
+          <t>27430</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>41336</t>
+          <t>41298</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>51,03%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16513</t>
+          <t>16184</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25042</t>
+          <t>24847</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20547</t>
+          <t>20443</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29447</t>
+          <t>29384</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40129</t>
+          <t>40430</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52447</t>
+          <t>52481</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,44%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7922</t>
+          <t>8117</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16451</t>
+          <t>16780</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7154</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16054</t>
+          <t>16158</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17118</t>
+          <t>17084</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>29436</t>
+          <t>29135</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>41,88%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24112</t>
+          <t>24302</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33892</t>
+          <t>34546</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22612</t>
+          <t>23508</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34701</t>
+          <t>34665</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50491</t>
+          <t>51100</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65862</t>
+          <t>65811</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>73,93%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7894</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17674</t>
+          <t>17484</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12528</t>
+          <t>12564</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24617</t>
+          <t>23721</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23153</t>
+          <t>23204</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>38524</t>
+          <t>37915</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>42,59%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>88690</t>
+          <t>89801</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>107012</t>
+          <t>108483</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>89414</t>
+          <t>88910</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>109213</t>
+          <t>109578</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>183996</t>
+          <t>182190</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>211302</t>
+          <t>210777</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,02%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39785</t>
+          <t>38314</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>58107</t>
+          <t>56996</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49361</t>
+          <t>48996</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69160</t>
+          <t>69664</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>94069</t>
+          <t>94594</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>121375</t>
+          <t>123181</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>40,34%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9827</t>
+          <t>10149</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18175</t>
+          <t>18417</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>6419</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15288</t>
+          <t>14999</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18984</t>
+          <t>19162</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31126</t>
+          <t>31178</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>64,24%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6184</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14532</t>
+          <t>14210</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8888</t>
+          <t>9177</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17164</t>
+          <t>17757</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17410</t>
+          <t>17358</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29552</t>
+          <t>29374</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>60,52%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19284</t>
+          <t>20005</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29315</t>
+          <t>29939</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20870</t>
+          <t>21391</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30909</t>
+          <t>30984</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44138</t>
+          <t>42971</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57943</t>
+          <t>57936</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>69,1%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13384</t>
+          <t>12760</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23415</t>
+          <t>22694</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10238</t>
+          <t>10163</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20277</t>
+          <t>19756</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>25910</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39708</t>
+          <t>40875</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>48,75%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16019</t>
+          <t>15818</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23168</t>
+          <t>23155</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9318</t>
+          <t>9145</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18084</t>
+          <t>17868</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27935</t>
+          <t>27466</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38899</t>
+          <t>38738</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>69,9%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4447</t>
+          <t>4460</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11596</t>
+          <t>11797</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9722</t>
+          <t>9938</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18488</t>
+          <t>18661</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16522</t>
+          <t>16683</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>27486</t>
+          <t>27955</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>50,44%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13973</t>
+          <t>14325</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23724</t>
+          <t>23908</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12587</t>
+          <t>12984</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21921</t>
+          <t>21569</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29999</t>
+          <t>29786</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42875</t>
+          <t>42578</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>67,65%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9064</t>
+          <t>8880</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18815</t>
+          <t>18463</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8225</t>
+          <t>8577</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17559</t>
+          <t>17162</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20059</t>
+          <t>20356</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32935</t>
+          <t>33148</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,67%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69181</t>
+          <t>68501</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87247</t>
+          <t>86885</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59106</t>
+          <t>58903</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77262</t>
+          <t>76857</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>134154</t>
+          <t>132523</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>158441</t>
+          <t>157678</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>62,89%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40214</t>
+          <t>40576</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>58280</t>
+          <t>58960</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46014</t>
+          <t>46419</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64170</t>
+          <t>64373</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>92296</t>
+          <t>93059</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>116583</t>
+          <t>118214</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>47,15%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13083</t>
+          <t>12728</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20899</t>
+          <t>20323</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13904</t>
+          <t>13954</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23238</t>
+          <t>22936</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29871</t>
+          <t>29773</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41895</t>
+          <t>41900</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,32%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4942</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12758</t>
+          <t>13113</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4422</t>
+          <t>4724</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13756</t>
+          <t>13706</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11606</t>
+          <t>11601</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23630</t>
+          <t>23728</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,35%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14195</t>
+          <t>13842</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29559</t>
+          <t>29459</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28954</t>
+          <t>29624</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43134</t>
+          <t>43441</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46809</t>
+          <t>48031</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67621</t>
+          <t>68435</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>63,34%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14683</t>
+          <t>14783</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30047</t>
+          <t>30400</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20675</t>
+          <t>20368</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>34855</t>
+          <t>34185</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>40430</t>
+          <t>39616</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>61242</t>
+          <t>60020</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>55,55%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22178</t>
+          <t>22408</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64689</t>
+          <t>66646</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23277</t>
+          <t>22869</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38472</t>
+          <t>38203</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55710</t>
+          <t>55613</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>102078</t>
+          <t>104233</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>77,79%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12382</t>
+          <t>10425</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54893</t>
+          <t>54663</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18451</t>
+          <t>18720</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33646</t>
+          <t>34054</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31916</t>
+          <t>29761</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>78284</t>
+          <t>78381</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>58,5%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16142</t>
+          <t>16587</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24653</t>
+          <t>24510</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15291</t>
+          <t>15913</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25204</t>
+          <t>25585</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34236</t>
+          <t>34770</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47339</t>
+          <t>47673</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>74,06%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5908</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14419</t>
+          <t>13974</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8605</t>
+          <t>8224</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18518</t>
+          <t>17896</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17031</t>
+          <t>16697</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>30134</t>
+          <t>29600</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>45,98%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>85233</t>
+          <t>85806</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>133075</t>
+          <t>131950</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>94726</t>
+          <t>95069</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>119965</t>
+          <t>120047</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>189045</t>
+          <t>191488</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>244269</t>
+          <t>243782</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,73%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44640</t>
+          <t>45765</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>92482</t>
+          <t>91909</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>62236</t>
+          <t>62154</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>87475</t>
+          <t>87132</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>115647</t>
+          <t>116134</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>170871</t>
+          <t>168428</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>46,8%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A01-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16A01-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,47 +723,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>32818</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>32818</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>32818</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>32818</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,47 +1066,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>41647</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>41647</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,47 +1409,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>25164</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>25164</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>25164</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>25164</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,47 +1752,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>25677</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>25677</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>25677</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>25677</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,47 +2095,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2675,67 +2675,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>21552</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16488</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>26111</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>62,61%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>47,9%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>75,85%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>23486</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19266</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>27148</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>18760</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>27009</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>74,69%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>61,27%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>86,33%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>21552</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>16411</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>25973</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>62,61%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38470</t>
+          <t>38159</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50845</t>
+          <t>50995</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,42%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12872</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8313</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17936</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>37,39%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>24,15%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>52,1%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>7960</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4298</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>12180</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>4437</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>12686</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>25,31%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>13,67%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>38,73%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>12872</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>8451</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>18013</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>37,39%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15025</t>
+          <t>14875</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27400</t>
+          <t>27711</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>42,07%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>34424</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>34424</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>34424</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>31446</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>31446</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>31446</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>34424</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>34424</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>34424</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>22472</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>16857</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>27594</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>55,73%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>41,81%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>68,44%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>24589</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>19417</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>29208</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>19251</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>29447</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>60,56%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>47,82%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>71,94%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>22472</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>17168</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>27827</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>55,73%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39623</t>
+          <t>38889</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53491</t>
+          <t>53910</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>66,62%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17848</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12726</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>23463</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>44,27%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>31,56%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>58,19%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>16012</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>11393</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>21184</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>11154</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>21350</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>39,44%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>28,06%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>52,18%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>17848</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>12493</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>23152</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>44,27%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>27430</t>
+          <t>27011</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>41298</t>
+          <t>42032</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>51,94%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>40320</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>40320</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>40320</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>40601</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>40601</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>40601</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>40320</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>40320</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>40320</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>25664</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>20458</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>29550</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>70,12%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>55,9%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>80,74%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>21072</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>16184</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>24847</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>16659</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>25073</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>63,93%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>49,1%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>75,38%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>25664</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>20443</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>29384</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>70,12%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40430</t>
+          <t>40700</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52481</t>
+          <t>52527</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,51%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10937</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>7051</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>16143</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>29,88%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>19,26%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>44,1%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>11892</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>8117</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>16780</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>7891</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>36,07%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>24,62%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>50,9%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>10937</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>7217</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>16158</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>29,88%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17084</t>
+          <t>17038</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>29135</t>
+          <t>28865</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,49%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>36601</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>36601</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>36601</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>32964</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>32964</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>32964</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>36601</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>36601</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>36601</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>29259</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>23134</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>34379</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>61,95%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>48,98%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>72,79%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>29539</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>24302</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>34546</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>24206</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>33982</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>70,69%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>58,16%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>82,67%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>29259</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>23508</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>34665</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>61,95%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51100</t>
+          <t>51293</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65811</t>
+          <t>66359</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>74,55%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>17970</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>12850</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>24095</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>38,05%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>27,21%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>51,02%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>12247</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>7240</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>17484</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>7804</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>17580</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>29,31%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>17,33%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>41,84%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>17970</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>12564</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>23721</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>38,05%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23204</t>
+          <t>22656</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37915</t>
+          <t>37722</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,38%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>47229</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>47229</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>47229</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>41786</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>41786</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>41786</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>47229</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>47229</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>47229</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>98947</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>88618</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>108340</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>62,4%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>55,88%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>68,32%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>98686</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>89801</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>108483</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>89108</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>107709</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>67,23%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>61,17%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>73,9%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>98947</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>88910</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>109578</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>62,4%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>182190</t>
+          <t>184488</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>210777</t>
+          <t>211108</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>69,13%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>59627</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>50234</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>69956</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>37,6%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>31,68%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>44,12%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>48111</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>38314</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>56996</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>39088</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>57689</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>32,77%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>26,1%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>38,83%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>59627</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>48996</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>69664</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>37,6%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>94594</t>
+          <t>94263</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>123181</t>
+          <t>120883</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>39,59%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>158574</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>158574</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>158574</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>146797</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>146797</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>146797</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>158574</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>158574</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>158574</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10580</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6202</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14732</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>43,76%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>25,65%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>60,94%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>14378</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10149</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18417</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>9657</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>18113</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>59,02%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>41,67%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>75,6%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>10580</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>6419</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>14999</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>43,76%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19162</t>
+          <t>19265</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31178</t>
+          <t>31016</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>63,9%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13596</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9444</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17974</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>56,24%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>39,06%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>74,35%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>9981</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5942</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14210</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>6246</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>14702</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>40,98%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>24,4%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>58,33%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>13596</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>9177</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>17757</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>56,24%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17358</t>
+          <t>17520</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29374</t>
+          <t>29271</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,31%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24176</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24176</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24176</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>24359</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>24359</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>24359</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>24176</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>24176</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>24176</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>26510</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>21238</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>31163</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>64,43%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>51,61%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>75,74%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>24782</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>20005</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>29939</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>19692</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>29893</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>58,04%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>46,85%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>70,12%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>26510</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>21391</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>30984</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>64,43%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42971</t>
+          <t>44328</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57936</t>
+          <t>58201</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>69,41%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14637</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9984</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>19909</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>35,57%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>24,26%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>48,39%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>17917</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>12760</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>22694</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>12806</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>23007</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>41,96%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>29,88%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>53,15%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>14637</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>10163</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>19756</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>35,57%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>25910</t>
+          <t>25645</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>40875</t>
+          <t>39518</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>47,13%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>41147</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>41147</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>41147</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>42699</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>42699</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>42699</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>41147</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>41147</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>41147</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13642</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9111</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17628</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>49,06%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>32,77%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>63,4%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>19908</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>15818</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>23155</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>16031</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>23011</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>72,09%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>57,28%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>83,85%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>13642</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>9145</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>17868</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>49,06%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27466</t>
+          <t>27849</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38738</t>
+          <t>39327</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>70,96%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>14164</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10178</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>18695</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>50,94%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>36,6%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>67,23%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>7707</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>4460</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>11797</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4604</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>11584</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>27,91%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>16,15%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>42,72%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>14164</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>9938</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>18661</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>50,94%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16683</t>
+          <t>16094</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>27955</t>
+          <t>27572</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>49,75%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>27806</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>27806</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>27806</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>27615</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>27615</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>27615</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>27806</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>27806</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>27806</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17246</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12125</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>21399</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>57,21%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>40,22%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>70,98%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>19144</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>14325</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>23908</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>14035</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>23566</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>58,39%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>43,69%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>72,92%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>17246</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>12984</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>21569</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>57,21%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29786</t>
+          <t>29941</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42578</t>
+          <t>42932</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>68,22%</t>
         </is>
       </c>
     </row>
@@ -5764,67 +5764,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>12900</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8747</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>18021</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>42,79%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>29,02%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>59,78%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>13644</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>8880</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>18463</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>9222</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>18753</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>41,61%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>27,08%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>56,31%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>12900</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>8577</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>17162</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>42,79%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20356</t>
+          <t>20002</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>33148</t>
+          <t>32993</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,43%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>30146</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>30146</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>30146</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>32788</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>32788</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>32788</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>30146</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>30146</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>30146</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>67979</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>58624</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>77455</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>55,14%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>47,55%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>62,83%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>78212</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>68501</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>86885</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>68124</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>86669</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>61,36%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>53,74%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>68,17%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>67979</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>58903</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>76857</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>55,14%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>132523</t>
+          <t>133087</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>157678</t>
+          <t>158295</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>63,13%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>55297</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>45821</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>64652</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>44,86%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>37,17%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>52,45%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>49249</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>40576</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>58960</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>40792</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>59337</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>38,64%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>31,83%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>46,26%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>55297</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>46419</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>64373</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>44,86%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>93059</t>
+          <t>92442</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>118214</t>
+          <t>117650</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>46,92%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>16952</t>
+          <t>17726</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12728</t>
+          <t>12485</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20323</t>
+          <t>20925</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19243</t>
+          <t>17437</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13954</t>
+          <t>13312</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22936</t>
+          <t>21131</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>36196</t>
+          <t>35163</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29773</t>
+          <t>29267</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41900</t>
+          <t>40210</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,95%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6896</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3697</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12137</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>28,01%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>15,01%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>49,29%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>8889</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5518</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>13113</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>34,4%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>21,35%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>50,74%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8417</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4724</t>
+          <t>5177</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13706</t>
+          <t>12996</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>17305</t>
+          <t>15766</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11601</t>
+          <t>10719</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23728</t>
+          <t>21662</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>42,53%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>25841</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>25841</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>25841</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>26308</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>26308</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>26308</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>50929</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>50929</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>50929</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>32741</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>26228</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>38632</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>57,99%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>46,46%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>68,43%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>22722</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>13842</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>29459</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>51,36%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>31,29%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>66,59%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36267</t>
+          <t>21190</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29624</t>
+          <t>16510</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43441</t>
+          <t>25621</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>58989</t>
+          <t>53931</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48031</t>
+          <t>46402</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68435</t>
+          <t>62107</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>67,07%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>23717</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>17826</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>30230</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>42,01%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>31,57%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>53,54%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>21520</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>14783</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>30400</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>48,64%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>33,41%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>68,71%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>27542</t>
+          <t>14946</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20368</t>
+          <t>10515</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>34185</t>
+          <t>19626</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>49062</t>
+          <t>38663</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39616</t>
+          <t>30487</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>60020</t>
+          <t>46192</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>49,89%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>44242</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>44242</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>44242</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>36136</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>36136</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>36136</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>108051</t>
+          <t>92594</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>108051</t>
+          <t>92594</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>108051</t>
+          <t>92594</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>29072</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>21367</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>35231</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>55,53%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>40,81%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>67,29%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>43507</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>22408</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>66646</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>56,45%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>29,07%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>86,47%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>31455</t>
+          <t>19595</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22869</t>
+          <t>13657</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38203</t>
+          <t>27306</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>74962</t>
+          <t>48667</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55613</t>
+          <t>39435</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104233</t>
+          <t>59233</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>57,41%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>23283</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>17124</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>30988</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>44,47%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>32,71%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>59,19%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>33564</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>10425</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>54663</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>43,55%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>13,53%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>70,93%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25468</t>
+          <t>31231</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18720</t>
+          <t>23520</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34054</t>
+          <t>37169</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>59032</t>
+          <t>54514</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29761</t>
+          <t>43948</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>78381</t>
+          <t>63746</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>61,78%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>133994</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>133994</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>133994</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>18623</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13886</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>23070</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>59,09%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>44,06%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>73,2%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>20837</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>16587</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>24510</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>68,18%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>54,28%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>80,2%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>19756</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15913</t>
+          <t>15217</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25585</t>
+          <t>23485</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>41433</t>
+          <t>38378</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34770</t>
+          <t>31545</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47673</t>
+          <t>44186</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>72,15%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>12894</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8447</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>17631</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>40,91%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>26,8%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>55,94%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>9724</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>6051</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>13974</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>31,82%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>19,8%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>45,72%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>13213</t>
+          <t>9967</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8224</t>
+          <t>6238</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17896</t>
+          <t>14506</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>22937</t>
+          <t>22862</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16697</t>
+          <t>17054</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29600</t>
+          <t>29695</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>48,49%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>98162</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>87974</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>110339</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>59,51%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>53,33%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>66,89%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>104018</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>85806</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>131950</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>58,53%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>48,28%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>74,25%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>107562</t>
+          <t>77978</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>95069</t>
+          <t>67490</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>120047</t>
+          <t>87349</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>211579</t>
+          <t>176140</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>191488</t>
+          <t>161358</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>243782</t>
+          <t>190697</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>61,93%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>66790</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>54613</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>76978</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>40,49%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>33,11%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>46,67%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>73697</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>45765</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>91909</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>41,47%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>25,75%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>51,72%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>74639</t>
+          <t>65014</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>62154</t>
+          <t>55643</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>87132</t>
+          <t>75502</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>148337</t>
+          <t>131804</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>116134</t>
+          <t>117247</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>168428</t>
+          <t>146586</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>47,6%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
